--- a/cadet_data/CadetData_PTG.xlsx
+++ b/cadet_data/CadetData_PTG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94a1dad5ec87e9ff/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94a1dad5ec87e9ff/Documents/Programming/A4Uniforms/cadet_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6871B3D2-A6BB-4B1D-A996-D218B7F7D479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6871B3D2-A6BB-4B1D-A996-D218B7F7D479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44D3DE53-4625-4145-8FC3-5D3182BEFA92}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9B60E73C-DEB2-4C6F-A981-6244C20FDCA6}"/>
   </bookViews>
@@ -47,33 +47,6 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>Shirt Size</t>
-  </si>
-  <si>
-    <t>Shirt Quantity</t>
-  </si>
-  <si>
-    <t>Short Size</t>
-  </si>
-  <si>
-    <t>Short Quantity</t>
-  </si>
-  <si>
-    <t>Jacket Size</t>
-  </si>
-  <si>
-    <t>Jacket Quantity</t>
-  </si>
-  <si>
-    <t>Pant Size</t>
-  </si>
-  <si>
-    <t>Pant Quantity</t>
-  </si>
-  <si>
-    <t>Allen, Michael</t>
-  </si>
-  <si>
     <t>AS100</t>
   </si>
   <si>
@@ -86,9 +59,6 @@
     <t>M/R</t>
   </si>
   <si>
-    <t>Calderon, Mia</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -98,33 +68,15 @@
     <t>S</t>
   </si>
   <si>
-    <t>Emmons, Mckenzie</t>
-  </si>
-  <si>
-    <t>Guttman, Ryan</t>
-  </si>
-  <si>
     <t>M/L</t>
   </si>
   <si>
-    <t>Kieselowsky, Sofiya</t>
-  </si>
-  <si>
     <t>S/S</t>
   </si>
   <si>
-    <t>Krenk, Spencer</t>
-  </si>
-  <si>
     <t>AS150</t>
   </si>
   <si>
-    <t>Roy, Ritika</t>
-  </si>
-  <si>
-    <t>Spurlock, Liam</t>
-  </si>
-  <si>
     <t>XXL</t>
   </si>
   <si>
@@ -134,217 +86,265 @@
     <t>3XL/R</t>
   </si>
   <si>
-    <t>Tsoi, Thomas</t>
-  </si>
-  <si>
-    <t>Anand, Hrishikesh</t>
-  </si>
-  <si>
     <t>AS200</t>
   </si>
   <si>
-    <t>Ben-Zvi, Ari</t>
-  </si>
-  <si>
     <t>L/R</t>
   </si>
   <si>
-    <t>Besana, Anastasia</t>
-  </si>
-  <si>
     <t>S/R</t>
   </si>
   <si>
-    <t>Chung, Ethan</t>
-  </si>
-  <si>
-    <t>Elnasser, Zaid</t>
-  </si>
-  <si>
-    <t>XL, XXL</t>
-  </si>
-  <si>
-    <t>1, 1</t>
-  </si>
-  <si>
     <t>XL</t>
   </si>
   <si>
     <t>XL/R</t>
   </si>
   <si>
-    <t>Gentile, Nicholas</t>
-  </si>
-  <si>
     <t>M/S</t>
   </si>
   <si>
-    <t>Gerst, Tyler</t>
-  </si>
-  <si>
     <t>AS250</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Gopalakrishnan, Laya</t>
-  </si>
-  <si>
-    <t>Harold, Danille</t>
-  </si>
-  <si>
     <t>AS500</t>
   </si>
   <si>
-    <t>Kelly, Connor</t>
-  </si>
-  <si>
-    <t>Maria, Antonio</t>
-  </si>
-  <si>
-    <t>McCarthy, Norah</t>
-  </si>
-  <si>
     <t>S/L</t>
   </si>
   <si>
-    <t>Miller, Kenneth</t>
-  </si>
-  <si>
-    <t>Nacanaynay, Jakob</t>
-  </si>
-  <si>
     <t>L/S</t>
   </si>
   <si>
-    <t>Park, Jekemiah</t>
-  </si>
-  <si>
-    <t>Racette, Nicholas</t>
-  </si>
-  <si>
-    <t>Smiley, Samuel</t>
-  </si>
-  <si>
-    <t>Sokolowski, James</t>
-  </si>
-  <si>
-    <t>Tama, Charlotte</t>
-  </si>
-  <si>
-    <t>Yap, Nicholas</t>
-  </si>
-  <si>
-    <t>Chaney, Jack</t>
-  </si>
-  <si>
     <t>AS300</t>
   </si>
   <si>
-    <t>Chung, Hanna</t>
-  </si>
-  <si>
-    <t>Fujimoto, Andrew</t>
-  </si>
-  <si>
-    <t>Marino, Frank</t>
-  </si>
-  <si>
-    <t>Martini, Marco</t>
-  </si>
-  <si>
-    <t>Martins, Anket</t>
-  </si>
-  <si>
-    <t>McBride, Lindsey</t>
-  </si>
-  <si>
-    <t>Melton, Dawson</t>
-  </si>
-  <si>
-    <t>Rahman, Nadia</t>
-  </si>
-  <si>
-    <t>XS/S, XS/R, S/R</t>
-  </si>
-  <si>
-    <t>1, 1, 1</t>
-  </si>
-  <si>
-    <t>Randall, Conrad</t>
-  </si>
-  <si>
-    <t>Shegogue, Thomas</t>
-  </si>
-  <si>
-    <t>Stallone, Thomas</t>
-  </si>
-  <si>
-    <t>Viani, Jared</t>
-  </si>
-  <si>
-    <t>Zegunia, Julia</t>
-  </si>
-  <si>
-    <t>Annor, Reginald</t>
-  </si>
-  <si>
     <t>AS400</t>
   </si>
   <si>
-    <t>Chilukuri, Sathya</t>
-  </si>
-  <si>
-    <t>Ettinger, Sophie</t>
-  </si>
-  <si>
-    <t>Fancher, Phillip</t>
-  </si>
-  <si>
-    <t>M, L</t>
-  </si>
-  <si>
-    <t>1, 2</t>
-  </si>
-  <si>
-    <t>Hunt, Elyse</t>
-  </si>
-  <si>
-    <t>Isaac, Charles</t>
-  </si>
-  <si>
-    <t>S, L</t>
-  </si>
-  <si>
-    <t>1, 3</t>
-  </si>
-  <si>
-    <t>Kim, Leo</t>
-  </si>
-  <si>
-    <t>Long, John</t>
-  </si>
-  <si>
-    <t>Perez, Rodrigo</t>
-  </si>
-  <si>
-    <t>Scalfani-Cohen, Andrew</t>
-  </si>
-  <si>
-    <t>Szymanski, Zoe</t>
-  </si>
-  <si>
-    <t>Teague, Katie</t>
-  </si>
-  <si>
-    <t>Tremel, Pulani</t>
-  </si>
-  <si>
     <t>KEY</t>
   </si>
   <si>
     <t>Missing</t>
+  </si>
+  <si>
+    <t>ShirtSize</t>
+  </si>
+  <si>
+    <t>ShirtQuantity</t>
+  </si>
+  <si>
+    <t>ShortSize</t>
+  </si>
+  <si>
+    <t>ShortQuantity</t>
+  </si>
+  <si>
+    <t>JacketSize</t>
+  </si>
+  <si>
+    <t>JacketQuantity</t>
+  </si>
+  <si>
+    <t>PantSize</t>
+  </si>
+  <si>
+    <t>PantQuantity</t>
+  </si>
+  <si>
+    <t>Allen,Michael</t>
+  </si>
+  <si>
+    <t>Calderon,Mia</t>
+  </si>
+  <si>
+    <t>Emmons,Mckenzie</t>
+  </si>
+  <si>
+    <t>Guttman,Ryan</t>
+  </si>
+  <si>
+    <t>Kieselowsky,Sofiya</t>
+  </si>
+  <si>
+    <t>Krenk,Spencer</t>
+  </si>
+  <si>
+    <t>Roy,Ritika</t>
+  </si>
+  <si>
+    <t>Spurlock,Liam</t>
+  </si>
+  <si>
+    <t>Tsoi,Thomas</t>
+  </si>
+  <si>
+    <t>Anand,Hrishikesh</t>
+  </si>
+  <si>
+    <t>Ben-Zvi,Ari</t>
+  </si>
+  <si>
+    <t>Besana,Anastasia</t>
+  </si>
+  <si>
+    <t>Chung,Ethan</t>
+  </si>
+  <si>
+    <t>Elnasser,Zaid</t>
+  </si>
+  <si>
+    <t>XL,XXL</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>Gentile,Nicholas</t>
+  </si>
+  <si>
+    <t>Gerst,Tyler</t>
+  </si>
+  <si>
+    <t>Gopalakrishnan,Laya</t>
+  </si>
+  <si>
+    <t>Harold,Danille</t>
+  </si>
+  <si>
+    <t>Kelly,Connor</t>
+  </si>
+  <si>
+    <t>Maria,Antonio</t>
+  </si>
+  <si>
+    <t>McCarthy,Norah</t>
+  </si>
+  <si>
+    <t>Miller,Kenneth</t>
+  </si>
+  <si>
+    <t>Nacanaynay,Jakob</t>
+  </si>
+  <si>
+    <t>Park,Jekemiah</t>
+  </si>
+  <si>
+    <t>Racette,Nicholas</t>
+  </si>
+  <si>
+    <t>Smiley,Samuel</t>
+  </si>
+  <si>
+    <t>Sokolowski,James</t>
+  </si>
+  <si>
+    <t>Tama,Charlotte</t>
+  </si>
+  <si>
+    <t>Yap,Nicholas</t>
+  </si>
+  <si>
+    <t>Chaney,Jack</t>
+  </si>
+  <si>
+    <t>Chung,Hanna</t>
+  </si>
+  <si>
+    <t>Fujimoto,Andrew</t>
+  </si>
+  <si>
+    <t>Marino,Frank</t>
+  </si>
+  <si>
+    <t>Martini,Marco</t>
+  </si>
+  <si>
+    <t>Martins,Anket</t>
+  </si>
+  <si>
+    <t>McBride,Lindsey</t>
+  </si>
+  <si>
+    <t>Melton,Dawson</t>
+  </si>
+  <si>
+    <t>Rahman,Nadia</t>
+  </si>
+  <si>
+    <t>XS/S,XS/R,S/R</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>Randall,Conrad</t>
+  </si>
+  <si>
+    <t>Shegogue,Thomas</t>
+  </si>
+  <si>
+    <t>Stallone,Thomas</t>
+  </si>
+  <si>
+    <t>Viani,Jared</t>
+  </si>
+  <si>
+    <t>Zegunia,Julia</t>
+  </si>
+  <si>
+    <t>Annor,Reginald</t>
+  </si>
+  <si>
+    <t>Chilukuri,Sathya</t>
+  </si>
+  <si>
+    <t>Ettinger,Sophie</t>
+  </si>
+  <si>
+    <t>Fancher,Phillip</t>
+  </si>
+  <si>
+    <t>M,L</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>Hunt,Elyse</t>
+  </si>
+  <si>
+    <t>Isaac,Charles</t>
+  </si>
+  <si>
+    <t>S,L</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>Kim,Leo</t>
+  </si>
+  <si>
+    <t>Long,John</t>
+  </si>
+  <si>
+    <t>Perez,Rodrigo</t>
+  </si>
+  <si>
+    <t>Scalfani-Cohen,Andrew</t>
+  </si>
+  <si>
+    <t>Szymanski,Zoe</t>
+  </si>
+  <si>
+    <t>Teague,Katie</t>
+  </si>
+  <si>
+    <t>Tremel,Pulani</t>
   </si>
 </sst>
 </file>
@@ -1035,79 +1035,79 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E2" s="7">
         <v>1</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G2" s="7">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="8" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E3" s="14">
         <v>1</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G3" s="14">
         <v>1</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E4" s="7">
         <v>1</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G4" s="7">
         <v>1</v>
@@ -1146,75 +1146,75 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E5" s="14">
         <v>1</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G5" s="14">
         <v>1</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="13" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E6" s="7">
         <v>1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G6" s="7">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="8" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
@@ -1227,127 +1227,127 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E8" s="7">
         <v>1</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G8" s="7">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="8" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="E9" s="14">
         <v>1</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G9" s="14">
         <v>1</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="13" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K9" s="14"/>
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E10" s="21">
         <v>1</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G10" s="21">
         <v>1</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="22" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E11" s="28">
         <v>1</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G11" s="28">
         <v>1</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I11" s="28">
         <v>1</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K11" s="28">
         <v>1</v>
@@ -1355,34 +1355,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E12" s="7">
         <v>1</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G12" s="7">
         <v>1</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I12" s="7">
         <v>1</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K12" s="7">
         <v>1</v>
@@ -1390,34 +1390,34 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D13" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="14">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="14">
-        <v>1</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="14">
-        <v>1</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>38</v>
-      </c>
       <c r="I13" s="14">
         <v>1</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K13" s="14">
         <v>1</v>
@@ -1425,34 +1425,34 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E14" s="7">
         <v>1</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G14" s="7">
         <v>1</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I14" s="7">
         <v>1</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K14" s="7">
         <v>1</v>
@@ -1460,34 +1460,34 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="K15" s="14">
         <v>1</v>
@@ -1495,34 +1495,34 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E16" s="7">
         <v>1</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G16" s="7">
         <v>1</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I16" s="7">
         <v>1</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="K16" s="7">
         <v>1</v>
@@ -1530,28 +1530,28 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
         <v>1</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G17" s="14">
         <v>1</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="I17" s="14">
         <v>1</v>
@@ -1563,34 +1563,34 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="7">
+        <v>1</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="7">
+        <v>1</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="7">
-        <v>1</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="7">
-        <v>1</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="K18" s="7">
         <v>1</v>
@@ -1598,34 +1598,34 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
         <v>1</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G19" s="14">
         <v>1</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I19" s="14">
         <v>1</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K19" s="14">
         <v>1</v>
@@ -1633,34 +1633,34 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E20" s="7">
         <v>1</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G20" s="7">
         <v>1</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
         <v>1</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K20" s="7">
         <v>1</v>
@@ -1668,22 +1668,22 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E21" s="14">
         <v>1</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G21" s="14">
         <v>1</v>
@@ -1695,34 +1695,34 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E22" s="7">
         <v>1</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G22" s="7">
         <v>1</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="I22" s="7">
         <v>1</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K22" s="7">
         <v>1</v>
@@ -1730,34 +1730,34 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E23" s="14">
         <v>1</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K23" s="14">
         <v>1</v>
@@ -1765,34 +1765,34 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E24" s="7">
         <v>1</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G24" s="7">
         <v>1</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="I24" s="7">
         <v>1</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K24" s="7">
         <v>1</v>
@@ -1800,22 +1800,22 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
         <v>1</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G25" s="14">
         <v>1</v>
@@ -1825,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K25" s="14">
         <v>1</v>
@@ -1833,22 +1833,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E26" s="7">
         <v>1</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G26" s="7">
         <v>1</v>
@@ -1860,34 +1860,34 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D27" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="14">
+        <v>1</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="14">
+        <v>1</v>
+      </c>
+      <c r="J27" s="13" t="s">
         <v>18</v>
-      </c>
-      <c r="E27" s="14">
-        <v>1</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="14">
-        <v>1</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="K27" s="14">
         <v>1</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E28" s="7">
         <v>1</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G28" s="7">
         <v>1</v>
@@ -1922,34 +1922,34 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D29" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>1</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="14">
-        <v>1</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>38</v>
-      </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K29" s="14">
         <v>1</v>
@@ -1957,34 +1957,34 @@
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="29" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E30" s="21">
         <v>1</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G30" s="21">
         <v>1</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I30" s="21">
         <v>1</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K30" s="21">
         <v>1</v>
@@ -1992,34 +1992,34 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E31" s="28">
         <v>1</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G31" s="28">
         <v>1</v>
       </c>
       <c r="H31" s="27" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I31" s="28">
         <v>1</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K31" s="28">
         <v>1</v>
@@ -2027,34 +2027,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E32" s="7">
         <v>1</v>
       </c>
       <c r="F32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="7">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G32" s="7">
-        <v>1</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="I32" s="7">
         <v>1</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K32" s="7">
         <v>1</v>
@@ -2062,34 +2062,34 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E33" s="14">
         <v>1</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K33" s="14">
         <v>1</v>
@@ -2097,22 +2097,22 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E34" s="7">
         <v>4</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G34" s="7">
         <v>4</v>
@@ -2122,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K34" s="7">
         <v>1</v>
@@ -2130,34 +2130,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E35" s="14">
         <v>2</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G35" s="14">
         <v>2</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I35" s="14">
         <v>1</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K35" s="14">
         <v>1</v>
@@ -2165,34 +2165,34 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E36" s="7">
         <v>1</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G36" s="7">
         <v>1</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
         <v>1</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K36" s="7">
         <v>1</v>
@@ -2200,34 +2200,34 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E37" s="14">
         <v>1</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G37" s="14">
         <v>1</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I37" s="14">
         <v>1</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K37" s="14">
         <v>1</v>
@@ -2235,34 +2235,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E38" s="7">
         <v>1</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G38" s="7">
         <v>1</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
         <v>1</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="K38" s="7">
         <v>1</v>
@@ -2270,34 +2270,34 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E39" s="14">
         <v>3</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G39" s="14">
         <v>3</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K39" s="14">
         <v>1</v>
@@ -2305,34 +2305,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E40" s="7">
         <v>1</v>
       </c>
       <c r="F40" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="7">
+        <v>1</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="7">
-        <v>1</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="I40" s="7">
         <v>1</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K40" s="7">
         <v>1</v>
@@ -2340,34 +2340,34 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14">
         <v>1</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G41" s="14">
         <v>1</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I41" s="14">
         <v>1</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K41" s="14">
         <v>1</v>
@@ -2375,34 +2375,34 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E42" s="7">
         <v>1</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G42" s="7">
         <v>1</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I42" s="7">
         <v>1</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K42" s="7">
         <v>1</v>
@@ -2410,34 +2410,34 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E43" s="14">
         <v>1</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G43" s="14">
         <v>1</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I43" s="14">
         <v>1</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K43" s="14">
         <v>1</v>
@@ -2445,34 +2445,34 @@
     </row>
     <row r="44" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E44" s="21">
         <v>1</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G44" s="21">
         <v>1</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I44" s="21">
         <v>1</v>
       </c>
       <c r="J44" s="20" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K44" s="21">
         <v>1</v>
@@ -2480,34 +2480,34 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E45" s="28">
         <v>4</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G45" s="28">
         <v>4</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I45" s="28">
         <v>1</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K45" s="28">
         <v>1</v>
@@ -2515,22 +2515,22 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E46" s="7">
         <v>3</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G46" s="7">
         <v>3</v>
@@ -2546,34 +2546,34 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E47" s="14">
         <v>4</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G47" s="14">
         <v>3</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I47" s="14">
         <v>1</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K47" s="14">
         <v>1</v>
@@ -2581,22 +2581,22 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G48" s="7">
         <v>3</v>
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K48" s="7">
         <v>1</v>
@@ -2614,34 +2614,34 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E49" s="14">
         <v>3</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G49" s="14">
         <v>3</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I49" s="14">
         <v>1</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K49" s="14">
         <v>1</v>
@@ -2649,34 +2649,34 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E50" s="7">
         <v>4</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I50" s="7">
         <v>1</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K50" s="7">
         <v>1</v>
@@ -2684,34 +2684,34 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E51" s="14">
         <v>3</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G51" s="14">
         <v>3</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I51" s="14">
         <v>1</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K51" s="14">
         <v>1</v>
@@ -2719,22 +2719,22 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E52" s="7">
         <v>3</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G52" s="7">
         <v>3</v>
@@ -2750,34 +2750,34 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E53" s="14">
         <v>1</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G53" s="14">
         <v>2</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I53" s="14">
         <v>1</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K53" s="14">
         <v>1</v>
@@ -2785,34 +2785,34 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E54" s="7">
         <v>2</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G54" s="7">
         <v>2</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I54" s="7">
         <v>1</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K54" s="7">
         <v>1</v>
@@ -2820,34 +2820,34 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E55" s="14">
         <v>3</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G55" s="14">
         <v>3</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I55" s="14">
         <v>1</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="K55" s="14">
         <v>1</v>
@@ -2855,34 +2855,34 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E56" s="7">
         <v>4</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G56" s="7">
         <v>4</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I56" s="7">
         <v>1</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K56" s="7">
         <v>1</v>
@@ -2890,34 +2890,34 @@
     </row>
     <row r="57" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B57" s="31" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D57" s="33" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E57" s="34">
         <v>3</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G57" s="34">
         <v>3</v>
       </c>
       <c r="H57" s="33" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I57" s="34">
         <v>1</v>
       </c>
       <c r="J57" s="33" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K57" s="34">
         <v>1</v>
@@ -2928,11 +2928,11 @@
     </row>
     <row r="59" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="37" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="B59" s="38"/>
       <c r="C59" s="37" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">

--- a/cadet_data/CadetData_PTG.xlsx
+++ b/cadet_data/CadetData_PTG.xlsx
@@ -689,25 +689,39 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>S/S</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>S/S</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
